--- a/SLSSV3 BoM.xlsx
+++ b/SLSSV3 BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://npluk-my.sharepoint.com/personal/james_edwards_npl_co_uk/Documents/Documents/SLSS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="8_{93ED6D48-6C45-4EA7-9344-3347BCEAFEC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B5F5F2B-6126-4BF8-BA42-A9B8271614E9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417155C7-FF31-4824-81CF-6BE96CF2BA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14955" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>No</t>
   </si>
@@ -54,6 +54,18 @@
   </si>
   <si>
     <t>Part number</t>
+  </si>
+  <si>
+    <t>PSU</t>
+  </si>
+  <si>
+    <t>24V 5A PSU brick</t>
+  </si>
+  <si>
+    <t>https://uk.rs-online.com/web/p/ac-dc-adapters/2837427?gb=a</t>
+  </si>
+  <si>
+    <t>283-7427</t>
   </si>
 </sst>
 </file>
@@ -468,6 +480,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H7" s="1"/>
     </row>

--- a/SLSSV3 BoM.xlsx
+++ b/SLSSV3 BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417155C7-FF31-4824-81CF-6BE96CF2BA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3A8842-906D-40C6-B89C-31E9D45A2AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>No</t>
   </si>
@@ -66,6 +66,18 @@
   </si>
   <si>
     <t>283-7427</t>
+  </si>
+  <si>
+    <t>https://uk.rs-online.com/web/p/peltier-modules/2172395</t>
+  </si>
+  <si>
+    <t>peltier</t>
+  </si>
+  <si>
+    <t>40x40mm 77w</t>
+  </si>
+  <si>
+    <t>217-2395</t>
   </si>
 </sst>
 </file>
@@ -500,6 +512,26 @@
         <v>9</v>
       </c>
     </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="H7" s="1"/>
     </row>

--- a/SLSSV3 BoM.xlsx
+++ b/SLSSV3 BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\je7\Documents\GitHub\SLSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A3A8842-906D-40C6-B89C-31E9D45A2AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93A9C10-F325-4F08-B1B1-1DB8EE923F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>No</t>
   </si>
@@ -78,13 +78,28 @@
   </si>
   <si>
     <t>217-2395</t>
+  </si>
+  <si>
+    <t>Assembly components</t>
+  </si>
+  <si>
+    <t>PCB components</t>
+  </si>
+  <si>
+    <t>Arduino</t>
+  </si>
+  <si>
+    <t>Arduino nano every (already present)</t>
+  </si>
+  <si>
+    <t>ABX00028-full-pinout.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,13 +115,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -122,12 +156,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -463,16 +500,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B2:H12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:H12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="12.81640625" customWidth="1"/>
-    <col min="4" max="4" width="16.7265625" customWidth="1"/>
-    <col min="6" max="6" width="55.7265625" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" customWidth="1"/>
+    <col min="4" max="4" width="33.5703125" customWidth="1"/>
+    <col min="6" max="6" width="55.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -492,7 +539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1</v>
       </c>
@@ -512,7 +559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2</v>
       </c>
@@ -532,22 +579,75 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5</v>
+      </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D12" s="2"/>
       <c r="F12" s="1"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F8" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SLSSV3 BoM.xlsx
+++ b/SLSSV3 BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\je7\Documents\GitHub\SLSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93A9C10-F325-4F08-B1B1-1DB8EE923F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F72661-5813-4B10-B3BF-C03F9167738D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>No</t>
   </si>
@@ -93,13 +93,22 @@
   </si>
   <si>
     <t>ABX00028-full-pinout.pdf</t>
+  </si>
+  <si>
+    <t>Monochrome 0.96 128x64 OLED Graphic Display - STEMMA QT : ID 326 : Adafruit Industries, Unique &amp; fun DIY electronics and kits</t>
+  </si>
+  <si>
+    <t>Screen</t>
+  </si>
+  <si>
+    <t>Adafruit monochrome OLED display</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +130,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Lucida Sans Unicode"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -156,7 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -165,6 +180,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -631,6 +647,21 @@
       <c r="B9">
         <v>2</v>
       </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="6">
+        <v>326</v>
+      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C10" s="2"/>
@@ -647,7 +678,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F8" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+    <hyperlink ref="F9" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/SLSSV3 BoM.xlsx
+++ b/SLSSV3 BoM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\je7\Documents\GitHub\SLSS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F72661-5813-4B10-B3BF-C03F9167738D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461927D0-B6A5-4C7A-9A03-50E22688E9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -517,15 +517,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
   <dimension ref="B1:H12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" customWidth="1"/>
-    <col min="6" max="6" width="55.7109375" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" customWidth="1"/>
+    <col min="4" max="4" width="33.54296875" customWidth="1"/>
+    <col min="6" max="6" width="55.7265625" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>14</v>
       </c>
@@ -535,7 +535,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -555,7 +555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>1</v>
       </c>
@@ -575,7 +575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>2</v>
       </c>
@@ -588,14 +588,14 @@
       <c r="E4">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
@@ -605,7 +605,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>0</v>
       </c>
@@ -626,7 +626,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>1</v>
       </c>
@@ -643,7 +643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>2</v>
       </c>
@@ -663,15 +663,15 @@
         <v>326</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="D12" s="2"/>
       <c r="F12" s="1"/>
     </row>
@@ -679,8 +679,9 @@
   <hyperlinks>
     <hyperlink ref="F8" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
     <hyperlink ref="F9" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{A0A63F22-757F-463A-BAC4-D32816C56DA8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/SLSSV3 BoM.xlsx
+++ b/SLSSV3 BoM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\Documents\SLSS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461927D0-B6A5-4C7A-9A03-50E22688E9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FECCDDF-A27F-43ED-B05E-5BD2C1AE8454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{0175BE9B-09DB-4935-9617-04C8C213D07E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>No</t>
   </si>
@@ -102,6 +102,18 @@
   </si>
   <si>
     <t>Adafruit monochrome OLED display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heatsink </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peltier </t>
+  </si>
+  <si>
+    <t>SFH3501-16L | SPREADFAST Heatsink, Universal Square Alu, 35 x 35 x 16mm | RS</t>
+  </si>
+  <si>
+    <t>184-6721</t>
   </si>
 </sst>
 </file>
@@ -171,7 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -181,6 +193,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -516,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3D4A7C-6DC5-428F-8E7D-79698D90EF4B}">
-  <dimension ref="B1:H12"/>
+  <dimension ref="B1:H14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="12.81640625" customWidth="1"/>
@@ -595,73 +609,36 @@
         <v>13</v>
       </c>
     </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="7">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" t="s">
-        <v>5</v>
-      </c>
       <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="6">
-        <v>326</v>
-      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C10" s="2"/>
@@ -669,19 +646,80 @@
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="F11" s="1"/>
+      <c r="B11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="D12" s="2"/>
-      <c r="F12" s="1"/>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="6">
+        <v>326</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F8" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
-    <hyperlink ref="F9" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
+    <hyperlink ref="F13" r:id="rId1" display="https://docs.arduino.cc/resources/pinouts/ABX00028-full-pinout.pdf" xr:uid="{36804345-AEB4-4E7D-9BC7-C81B0111FE34}"/>
+    <hyperlink ref="F14" r:id="rId2" location="technical-details" display="https://www.adafruit.com/product/326 - technical-details" xr:uid="{4DCB4C25-963E-47BD-BBC1-72406EC1CDC3}"/>
     <hyperlink ref="F4" r:id="rId3" xr:uid="{A0A63F22-757F-463A-BAC4-D32816C56DA8}"/>
+    <hyperlink ref="F5" r:id="rId4" display="https://uk.rs-online.com/web/p/heatsinks/1846721?searchId=099ba976-54d0-4342-b192-1b402f10c554" xr:uid="{A833AD01-FDAC-4149-BCB2-C5DB47F070A0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>